--- a/KatalonData/ABPTestDataDemo/PaymentsACH_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/PaymentsACH_Demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{C446B2E9-24AE-481E-B3AC-9E92036919B5}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{88D7FCC8-A69A-4668-995A-3F612DF8B435}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="21" firstSheet="21" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
+    <workbookView activeTab="38" firstSheet="37" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
   </bookViews>
   <sheets>
     <sheet name="VerifySuccessfulPaymentPSNoCF" r:id="rId1" sheetId="1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="107">
   <si>
     <t>Result</t>
   </si>
@@ -213,82 +213,7 @@
     <t>NumberOfPayments</t>
   </si>
   <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 918-152028,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPdoubleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	Imtiaz,
-Last Name:,	Ahmed,
-Routing Number:,	****2691,
-Account Number:	,****5489,
-Billing Address:,	1853 Mandan Terace,
-Greenbelt, Maryland MD 20770,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $</t>
-  </si>
-  <si>
     <t>Deferred</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 918-152028,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPdoubleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	Imtiaz,
-Last Name:,	Ahmed,
-Routing Number:,	****2691,
-Account Number:	,****5489,
-Billing Address:,	1853 Mandan Terace,
-Greenbelt, Maryland MD 20770,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 918-152028,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPdoubleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	Imtiaz,
-Last Name:,	Ahmed,
-Routing Number:,	****2691,
-Account Number:	,****5489,
-Billing Address:,	1853 Mandan Terace,
-Greenbelt, Maryland MD 20770,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,
@@ -340,30 +265,6 @@
 4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
   </si>
   <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 918-152028,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPdoubleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	Imtiaz,
-Last Name:,	Ahmed,
-Routing Number:,	****4974,
-Account Number:	,****8307,
-Billing Address:,	1853 Mandan Terace,
-Greenbelt, Maryland MD 20770,
-Country:,	UNITED STATES,
-Account Type:,	Personal Savings,
-3. Payment Plan Information,
-Payment Plan Type:,	Automatic Payment 
-Payment Plan Start Date:,	
-4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
-  </si>
-  <si>
     <t>Tue Oct 14 16:46:22 IST 2025</t>
   </si>
   <si>
@@ -374,12 +275,6 @@
 Payment Method,Company Name:,First Name:,Last Name:,Routing Number:,Account Number:,Business Tax ID:,Billing Address:,Country:,Account Type:,</t>
   </si>
   <si>
-    <t>Sun Oct 26 17:47:04 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 19:09:11 IST 2025</t>
-  </si>
-  <si>
     <t>Sun Oct 26 19:32:00 IST 2025</t>
   </si>
   <si>
@@ -422,9 +317,6 @@
     <t>Thu Oct 30 10:38:03 IST 2025</t>
   </si>
   <si>
-    <t>Thu Oct 30 10:47:10 IST 2025</t>
-  </si>
-  <si>
     <t>Thu Oct 30 10:50:15 IST 2025</t>
   </si>
   <si>
@@ -432,58 +324,6 @@
   </si>
   <si>
     <t>Thu Oct 30 10:51:12 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Oct 31 15:15:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Oct 31 16:14:05 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Oct 31 16:22:36 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 03 22:43:14 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 12 21:41:42 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 13 21:13:29 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 13 21:20:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 918-152028,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPdoubleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	Imtiaz,
-Last Name:,	Ahmed,
-Routing Number:,	****2691,
-Account Number:	,****5489,
-Billing Address:,	1853 Mandan Terace,
-Greenbelt, Maryland MD 20770,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $</t>
-  </si>
-  <si>
-    <t>Thu Nov 13 22:05:48 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 17 18:54:39 IST 2025</t>
   </si>
   <si>
     <t>Mon Nov 17 22:53:43 IST 2025</t>
@@ -625,9 +465,6 @@
 United States</t>
   </si>
   <si>
-    <t>Thu Dec 18 00:15:01 IST 2025</t>
-  </si>
-  <si>
     <t>Personal Checking,
 ****4567,Billing Address:,
 1853 Mandan Terace,
@@ -638,9 +475,6 @@
     <t>Thu Dec 18 00:39:10 IST 2025</t>
   </si>
   <si>
-    <t>Thu Dec 18 00:46:51 IST 2025</t>
-  </si>
-  <si>
     <t>Personal Savings,
 ****345,Billing Address:,
 1853 Mandan Terace,
@@ -648,34 +482,177 @@
 United States</t>
   </si>
   <si>
+    <t>Thu Dec 18 13:02:00 IST 2025</t>
+  </si>
+  <si>
+    <t>Thu Dec 18 22:38:23 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 16:56:19 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 17:00:01 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 18:06:53 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 18:16:36 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 18:21:31 IST 2025</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6211-403001,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
+AutoABPDemoBBGDCF6211,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3 data,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	TABATHA,
+Last Name:,	MCGALLIARD,
+Routing Number:,	****2691,
+Account Number:	,****7541,
+Billing Address:,	1645 FOX ST,
+Concover, New York NY 28613,
+Country:,	UNITED STATES,
+Account Type:,	Personal Checking,
+3. Payment Plan Information,
+Payment Plan Type:,	Installment Plan,
+Payment Plan Duration:,	Daily,
+Payment Plan Start Date:,	
+4. Payment Plan,1 Daily payment of $</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 23:35:29 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 30 00:24:41 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 30 00:29:41 IST 2025</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6211-403001,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
+AutoABPDemoBBGDCF6211,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3 data,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	TABATHA,
+Last Name:,	MCGALLIARD,
+Routing Number:,	****2691,
+Account Number:	,****7541,
+Billing Address:,	1645 FOX ST,
+Concover, New York NY 28613,
+Country:,	UNITED STATES,
+Account Type:,	Personal Checking,
+3. Payment Plan Information,
+Payment Plan Type:,	Installment Plan,
+Payment Plan Duration:,	Deferred,
+Payment Plan Start Date:,	
+4. Payment Plan,1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t>Tue Dec 30 20:58:19 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 30 21:06:00 IST 2025</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6211-403001,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
+AutoABPDemoBBGDCF6211,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3 data,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	TABATHA,
+Last Name:,	MCGALLIARD,
+Routing Number:,	****2691,
+Account Number:	,****7541,
+Billing Address:,	1645 FOX ST,
+Concover, New York NY 28613,
+Country:,	UNITED STATES,
+Account Type:,	Personal Checking,
+3. Payment Plan Information,
+Payment Plan Type:,	Recurring,
+Payment Plan Duration:,	Daily,
+Payment Plan Start Date:,	
+4. Payment Plan, Daily payments of $</t>
+  </si>
+  <si>
+    <t>Tue Dec 30 21:12:06 IST 2025</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6211-403001,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
+AutoABPDemoBBGDCF6211,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3 data,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	TABATHA,
+Last Name:,	MCGALLIARD,
+Routing Number:,	****2691,
+Account Number:	,****7541,
+Billing Address:,	1645 FOX ST,
+Concover, New York NY 28613,
+Country:,	UNITED STATES,
+Account Type:,	Personal Checking,
+3. Payment Plan Information,
+Payment Plan Type:,	Recurring,
+Payment Plan Duration:,	Deferred,
+Payment Plan Start Date:,	
+4. Payment Plan,1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t>Tue Dec 30 21:24:30 IST 2025</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6211-403001,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
+AutoABPDemoBBGDCF6211,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3 data,
+UDF4:,	udf data4,
+2. Payment Method,
+Company Name:,	Vaddahun Corp,
+First Name:,	TABATHA,
+Last Name:,	MCGALLIARD,
+Routing Number:,	****2691,
+Account Number:	,****5489,
+Billing Address:,	1645 FOX ST,
+Concover, New York NY 28613,
+Country:,	UNITED STATES,
+Account Type:,	Personal Savings,
+3. Payment Plan Information,
+Payment Plan Type:,	Automatic Payment 
+Payment Plan Start Date:,	
+4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Thu Dec 18 00:50:01 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 18 00:52:48 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 18 00:54:06 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 18 12:57:25 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 18 12:59:31 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 18 13:02:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 18 15:04:45 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 18 15:20:02 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 18 22:38:23 IST 2025</t>
+    <t>Wed Dec 31 16:34:19 IST 2025</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1113,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1218,7 +1195,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1322,7 +1299,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1409,7 +1386,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1445,7 +1422,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1534,7 +1511,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1573,7 +1550,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1603,7 +1580,7 @@
         <v>10</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1665,7 +1642,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1755,7 +1732,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1845,7 +1822,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1935,7 +1912,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2025,7 +2002,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2149,19 +2126,19 @@
         <v>6</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="M2" s="13">
         <v>28601</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="O2" s="13" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2211,7 +2188,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2326,19 +2303,19 @@
         <v>6</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="M2" s="11">
         <v>28601</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2435,19 +2412,19 @@
         <v>6</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="M2" s="13">
         <v>28601</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="O2" s="13" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2516,7 +2493,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2541,13 +2518,13 @@
         <v>6</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
       <c r="N2" s="14"/>
       <c r="O2" s="14" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2616,7 +2593,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2641,13 +2618,13 @@
         <v>6</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
       <c r="N2" s="14"/>
       <c r="O2" s="14" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2719,7 +2696,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2744,13 +2721,13 @@
         <v>6</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
       <c r="N2" s="14"/>
       <c r="O2" s="14" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2800,7 +2777,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2872,7 +2849,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2950,7 +2927,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -2973,7 +2950,7 @@
         <v>6</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3023,7 +3000,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3101,7 +3078,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3124,7 +3101,7 @@
         <v>6</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -3174,7 +3151,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3251,7 +3228,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3281,7 +3258,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -3308,7 +3285,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -3381,7 +3358,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3404,7 +3381,7 @@
         <v>6</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3419,6 +3396,7 @@
   <cols>
     <col min="9" max="9" bestFit="true" customWidth="true" width="20.453125" collapsed="true"/>
     <col min="10" max="10" bestFit="true" customWidth="true" width="20.90625" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" width="10.26953125" collapsed="true"/>
   </cols>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -3476,7 +3454,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3502,43 +3480,43 @@
         <v>39</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="L2" s="7" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>12/19/2025</v>
+        <v>01/01/2026</v>
       </c>
       <c r="M2" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N2" s="17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O2" s="18" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 918-152028,
+Remittance ID: 6211-403001,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPdoubleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
+AutoABPDemoBBGDCF6211,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
-UDF3:,	udf3,
+UDF3:,	udf3 data,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	Imtiaz,
-Last Name:,	Ahmed,
+First Name:,	TABATHA,
+Last Name:,	MCGALLIARD,
 Routing Number:,	****2691,
-Account Number:	,****5489,
-Billing Address:,	1853 Mandan Terace,
-Greenbelt, Maryland MD 20770,
+Account Number:	,****7541,
+Billing Address:,	1645 FOX ST,
+Concover, New York NY 28613,
 Country:,	UNITED STATES,
 Account Type:,	Personal Checking,
 3. Payment Plan Information,
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 12/19/2025,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 5.00 starting on 12/19/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $12.00 on 01/01/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/01/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3546,7 +3524,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 5.00 starting on 12/19/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/01/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3622,7 +3600,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3648,43 +3626,43 @@
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="L2" s="7" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>12/19/2025</v>
+        <v>01/01/2026</v>
       </c>
       <c r="M2" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N2" s="17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O2" s="18" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 918-152028,
+Remittance ID: 6211-403001,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPdoubleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
+AutoABPDemoBBGDCF6211,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
-UDF3:,	udf3,
+UDF3:,	udf3 data,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	Imtiaz,
-Last Name:,	Ahmed,
+First Name:,	TABATHA,
+Last Name:,	MCGALLIARD,
 Routing Number:,	****2691,
-Account Number:	,****5489,
-Billing Address:,	1853 Mandan Terace,
-Greenbelt, Maryland MD 20770,
+Account Number:	,****7541,
+Billing Address:,	1645 FOX ST,
+Concover, New York NY 28613,
 Country:,	UNITED STATES,
 Account Type:,	Personal Checking,
 3. Payment Plan Information,
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 12/19/2025,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 5.00 starting on 12/19/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $12.00 on 01/01/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/01/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3692,7 +3670,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 5.00 starting on 12/19/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/01/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3762,7 +3740,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3782,49 +3760,49 @@
         <v>38</v>
       </c>
       <c r="I2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="L2" s="7" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>12/19/2025</v>
+        <v>01/01/2026</v>
       </c>
       <c r="M2" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N2" s="17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O2" s="18" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 918-152028,
+Remittance ID: 6211-403001,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPdoubleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
+AutoABPDemoBBGDCF6211,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
-UDF3:,	udf3,
+UDF3:,	udf3 data,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	Imtiaz,
-Last Name:,	Ahmed,
+First Name:,	TABATHA,
+Last Name:,	MCGALLIARD,
 Routing Number:,	****2691,
-Account Number:	,****5489,
-Billing Address:,	1853 Mandan Terace,
-Greenbelt, Maryland MD 20770,
+Account Number:	,****7541,
+Billing Address:,	1645 FOX ST,
+Concover, New York NY 28613,
 Country:,	UNITED STATES,
 Account Type:,	Personal Checking,
 3. Payment Plan Information,
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 12/19/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 5.00 starting on 12/19/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $12.00 on 01/01/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/01/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3832,7 +3810,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 5.00 starting on 12/19/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/01/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3902,7 +3880,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3922,49 +3900,49 @@
         <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="L2" s="7" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>12/19/2025</v>
+        <v>01/01/2026</v>
       </c>
       <c r="M2" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N2" s="17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O2" s="18" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 918-152028,
+Remittance ID: 6211-403001,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPdoubleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
+AutoABPDemoBBGDCF6211,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
-UDF3:,	udf3,
+UDF3:,	udf3 data,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	Imtiaz,
-Last Name:,	Ahmed,
+First Name:,	TABATHA,
+Last Name:,	MCGALLIARD,
 Routing Number:,	****2691,
-Account Number:	,****5489,
-Billing Address:,	1853 Mandan Terace,
-Greenbelt, Maryland MD 20770,
+Account Number:	,****7541,
+Billing Address:,	1645 FOX ST,
+Concover, New York NY 28613,
 Country:,	UNITED STATES,
 Account Type:,	Personal Checking,
 3. Payment Plan Information,
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 12/19/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 5.00 starting on 12/19/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $12.00 on 01/01/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/01/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3972,7 +3950,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 5.00 starting on 12/19/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/01/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4042,7 +4020,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4068,43 +4046,43 @@
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="L2" s="7" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>12/19/2025</v>
+        <v>01/01/2026</v>
       </c>
       <c r="M2" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N2" s="17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O2" s="18" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 918-152028,
+Remittance ID: 6211-403001,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPdoubleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
+AutoABPDemoBBGDCF6211,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
-UDF3:,	udf3,
+UDF3:,	udf3 data,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	Imtiaz,
-Last Name:,	Ahmed,
+First Name:,	TABATHA,
+Last Name:,	MCGALLIARD,
 Routing Number:,	****2691,
-Account Number:	,****5489,
-Billing Address:,	1853 Mandan Terace,
-Greenbelt, Maryland MD 20770,
+Account Number:	,****7541,
+Billing Address:,	1645 FOX ST,
+Concover, New York NY 28613,
 Country:,	UNITED STATES,
 Account Type:,	Personal Checking,
 3. Payment Plan Information,
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 12/19/2025,A Convenience Fee will be added to each transaction issued for Daily payment of 5.00 starting on 12/19/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $12.00 starting on 01/01/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/01/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4112,7 +4090,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 5.00 starting on 12/19/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/01/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4182,7 +4160,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4208,11 +4186,11 @@
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L2" s="7" t="str">
         <f ca="1">TEXT(TODAY(),"mm/dd/yyyy")</f>
-        <v>12/18/2025</v>
+        <v>12/31/2025</v>
       </c>
       <c r="M2" s="16">
         <v>10</v>
@@ -4298,7 +4276,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4324,11 +4302,11 @@
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L2" s="7" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>12/19/2025</v>
+        <v>01/01/2026</v>
       </c>
       <c r="M2" s="16">
         <v>10</v>
@@ -4414,7 +4392,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4440,17 +4418,17 @@
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="L2" s="7" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>12/19/2025</v>
+        <v>01/01/2026</v>
       </c>
       <c r="M2" s="16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N2" s="17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O2" s="18"/>
       <c r="P2" s="19" t="str">
@@ -4509,7 +4487,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4581,7 +4559,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4653,7 +4631,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4725,7 +4703,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4797,7 +4775,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4869,7 +4847,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestDataDemo/PaymentsACH_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/PaymentsACH_Demo.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="110">
   <si>
     <t>Result</t>
   </si>
@@ -653,6 +653,15 @@
   </si>
   <si>
     <t>Wed Dec 31 16:34:19 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 23:21:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 23:22:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 23:22:54 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3228,7 +3237,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3258,7 +3267,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -3285,7 +3294,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>

--- a/KatalonData/ABPTestDataDemo/PaymentsACH_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/PaymentsACH_Demo.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="147">
   <si>
     <t>Result</t>
   </si>
@@ -662,6 +662,117 @@
   </si>
   <si>
     <t>Tue Jan 06 23:22:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 18:16:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 18:17:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 18:18:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:22:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:23:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:24:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:14:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:16:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:16:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:17:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:17:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:18:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:19:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:19:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 23:59:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:00:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:20:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:21:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:22:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:23:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:24:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:24:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:25:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:26:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:27:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:27:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:28:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:29:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:30:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:31:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:31:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:32:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:33:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:34:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:51:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:52:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:52:47 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1118,11 +1229,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>91</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>122</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1158,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82449780-E031-48D5-B77A-C70DBD60E099}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:12" x14ac:dyDescent="0.35">
@@ -1200,10 +1311,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>53</v>
       </c>
       <c r="C2" s="3"/>
@@ -1262,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC1CCD5-A824-46D1-8E03-288885AFD37A}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:12" x14ac:dyDescent="0.35">
@@ -1304,10 +1415,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>52</v>
       </c>
       <c r="C2" s="3"/>
@@ -1346,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A041BDF5-260D-4C88-9BE9-34D621669BA2}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" customWidth="true" width="9.81640625" collapsed="true"/>
@@ -1391,10 +1502,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C2" s="3"/>
@@ -1427,10 +1538,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>51</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1468,7 +1579,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7731992D-7881-48D0-9061-1E14905AC37D}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="13" max="13" customWidth="true" width="28.36328125" collapsed="true"/>
@@ -1516,10 +1627,10 @@
       </c>
     </row>
     <row ht="188.5" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>47</v>
       </c>
       <c r="C2" s="3"/>
@@ -1555,10 +1666,10 @@
       </c>
     </row>
     <row ht="188.5" r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1599,7 +1710,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206DC968-58D8-4DD0-BC82-DF0CD0921B92}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="13" max="13" customWidth="true" width="17.1796875" collapsed="true"/>
@@ -1647,10 +1758,10 @@
       </c>
     </row>
     <row ht="261" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>59</v>
       </c>
       <c r="C2" s="3"/>
@@ -1692,7 +1803,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17981BF-ECA3-4B3E-BBE1-4117F8134390}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -1737,10 +1848,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>58</v>
       </c>
       <c r="C2" s="3"/>
@@ -1782,7 +1893,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51944D1B-9B45-4F14-94B4-232A04139A52}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -1827,10 +1938,10 @@
       </c>
     </row>
     <row ht="377" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>55</v>
       </c>
       <c r="C2" s="3"/>
@@ -1872,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125BE5F4-6DCB-4B74-965A-2A1B8749D9E8}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -1917,10 +2028,10 @@
       </c>
     </row>
     <row ht="377" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>56</v>
       </c>
       <c r="C2" s="3"/>
@@ -1962,7 +2073,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0885A1C1-EAD3-4FBD-9595-596BAA6EA611}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -2007,10 +2118,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>54</v>
       </c>
       <c r="C2" s="3"/>
@@ -2052,7 +2163,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C0D33A-2EC8-4BF6-B54B-4E680640D2E6}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="29.1796875" collapsed="true"/>
@@ -2157,7 +2268,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A814AFF7-515F-465B-94F7-1ECECB99CB8C}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2193,11 +2304,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>92</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>123</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2229,7 +2340,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418C9335-5599-4DF8-B9E1-DC0D08A18354}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="22.453125" collapsed="true"/>
@@ -2334,7 +2445,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E68741B-6F05-455D-9A92-FE831FDDA104}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="10" style="11" width="8.7265625" collapsed="true"/>
@@ -2443,7 +2554,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626903B0-5C9F-484A-9B05-1DD0B9C0F68E}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.7265625" collapsed="true"/>
@@ -2498,11 +2609,11 @@
       </c>
     </row>
     <row ht="87" r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>115</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2543,7 +2654,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3FAD2F-9501-4262-B6DA-9C1FC4650EB6}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="22.453125" collapsed="true"/>
@@ -2598,11 +2709,11 @@
       </c>
     </row>
     <row ht="101.5" r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>84</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>114</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2643,7 +2754,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38FF3975-D7A9-43F6-BD06-BA179809991B}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" customWidth="true" width="12.26953125" collapsed="true"/>
@@ -2701,11 +2812,11 @@
       </c>
     </row>
     <row ht="72.5" r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>87</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>113</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2746,7 +2857,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E02F51-555B-49C2-8C54-78632D6874FA}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2782,10 +2893,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>65</v>
       </c>
       <c r="C2" s="3"/>
@@ -2818,7 +2929,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37C3328-39C9-41FD-9DB4-ADF86208FC39}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2854,10 +2965,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>66</v>
       </c>
       <c r="C2" s="3"/>
@@ -2890,7 +3001,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C3A691B-8A11-403A-A18C-0B3D16CACD43}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="36.453125" collapsed="true"/>
@@ -2932,10 +3043,10 @@
       </c>
     </row>
     <row customHeight="1" ht="165.5" r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>79</v>
       </c>
       <c r="C2" s="3"/>
@@ -2969,7 +3080,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37656D7C-21ED-46B0-BCCF-CB4452FF881C}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -3005,10 +3116,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>64</v>
       </c>
       <c r="C2" s="3"/>
@@ -3041,7 +3152,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFDC152B-B1BC-4655-9345-694EE576670D}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="48.54296875" collapsed="true"/>
@@ -3083,10 +3194,10 @@
       </c>
     </row>
     <row customHeight="1" ht="201" r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>77</v>
       </c>
       <c r="C2" s="3"/>
@@ -3120,7 +3231,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDEF0D9-E05F-45C5-8D9F-25228B1275D2}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -3156,10 +3267,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>63</v>
       </c>
       <c r="C2" s="3"/>
@@ -3192,7 +3303,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6039023C-1CA6-42DC-810C-1BD4192BEEFE}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" bestFit="true" customWidth="true" width="13.90625" collapsed="true"/>
@@ -3222,22 +3333,22 @@
       <c r="G1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>107</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>144</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3249,25 +3360,25 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f xml:space="preserve"> "Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H2" t="str" s="0">
         <f xml:space="preserve"> "InstallmentPlan"</f>
         <v>InstallmentPlan</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I2" t="str" s="0">
         <f xml:space="preserve"> "Daily"</f>
         <v>Daily</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>108</v>
+      <c r="A3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>145</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -3278,23 +3389,23 @@
       <c r="F3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G3" t="str" s="0">
         <f ref="G3:G4" si="0" t="shared" xml:space="preserve"> "Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>109</v>
+      <c r="A4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>146</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -3305,11 +3416,11 @@
       <c r="F4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G4" t="str" s="0">
         <f si="0" t="shared"/>
         <v>Carlos</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="0">
         <v>35</v>
       </c>
     </row>
@@ -3321,7 +3432,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57CC2B03-4328-41F8-892F-CD81F2306003}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="30.36328125" collapsed="true"/>
@@ -3363,10 +3474,10 @@
       </c>
     </row>
     <row ht="130.5" r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>81</v>
       </c>
       <c r="C2" s="3"/>
@@ -3400,7 +3511,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55622C3-FD59-462E-B48B-E29C12630952}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="9" max="9" bestFit="true" customWidth="true" width="20.453125" collapsed="true"/>
@@ -3430,13 +3541,13 @@
       <c r="G1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>37</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -3459,11 +3570,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>94</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>124</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3475,17 +3586,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>39</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -3545,7 +3656,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2219A53-CA02-4D9A-9DD5-DA00AC5C4A23}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="10" max="10" bestFit="true" customWidth="true" width="20.90625" collapsed="true"/>
@@ -3576,13 +3687,13 @@
       <c r="G1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>37</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -3605,11 +3716,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>99</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>130</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3621,17 +3732,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -3691,7 +3802,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F61DCC56-CE37-4DAE-9D92-37CB9C481C7F}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -3716,13 +3827,13 @@
       <c r="G1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>37</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -3745,11 +3856,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>98</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>134</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3761,17 +3872,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -3831,7 +3942,7 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811FF27C-D0FF-4DEB-9DD7-F2E87A7294CB}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -3856,13 +3967,13 @@
       <c r="G1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>37</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -3885,11 +3996,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>103</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>142</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3901,17 +4012,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -3971,7 +4082,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D06A526-F613-4F63-B541-7FF18EFD935D}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -3996,13 +4107,13 @@
       <c r="G1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>37</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4025,11 +4136,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>101</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>138</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4041,17 +4152,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -4111,7 +4222,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02109C6A-9E4E-4705-AE64-D5133AE96048}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -4136,13 +4247,13 @@
       <c r="G1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>37</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4165,11 +4276,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>96</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>126</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4181,17 +4292,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -4224,7 +4335,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7CE9CCC-95AD-4B48-9052-C4AAA33A463F}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="27.7265625" collapsed="true"/>
@@ -4252,13 +4363,13 @@
       <c r="G1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>37</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4281,11 +4392,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>95</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>125</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4297,17 +4408,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -4340,7 +4451,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DEB38C-C9EF-4355-A944-36732259D0F6}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="25.6328125" collapsed="true"/>
@@ -4368,13 +4479,13 @@
       <c r="G1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>37</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4397,11 +4508,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>106</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>143</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4413,17 +4524,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -4456,7 +4567,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A973579-5DFF-4678-B07A-68B908946F3C}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -4492,10 +4603,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>61</v>
       </c>
       <c r="C2" s="3"/>
@@ -4528,7 +4639,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFFBF56E-14AC-4995-9D06-ECEAEC4D7822}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -4564,11 +4675,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>120</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4600,7 +4711,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A0D3B4-E6B2-45F0-8319-7F7FECCF3BD4}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -4636,11 +4747,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>90</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>119</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4672,7 +4783,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{777701B4-BB5E-43A1-B36C-41C7E1286146}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -4708,10 +4819,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>60</v>
       </c>
       <c r="C2" s="3"/>
@@ -4744,7 +4855,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382225BB-FBC4-4803-99D7-28B6A923E6A2}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -4780,11 +4891,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>89</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4816,7 +4927,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B8D28A0-6595-433A-95CB-C2AAB29F36D2}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -4852,11 +4963,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>88</v>
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>117</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestDataDemo/PaymentsACH_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/PaymentsACH_Demo.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="155">
   <si>
     <t>Result</t>
   </si>
@@ -773,6 +773,30 @@
   </si>
   <si>
     <t>Tue Jul 07 00:52:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:48:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:50:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 16:01:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 15:08:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:47:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:49:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:50:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:52:29 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1539,10 +1563,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -3047,7 +3071,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3198,7 +3222,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3478,7 +3502,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3720,7 +3744,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3860,7 +3884,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4000,7 +4024,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4140,7 +4164,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
